--- a/ksoft/docs/records/Stock_Group_Accounts.xlsx
+++ b/ksoft/docs/records/Stock_Group_Accounts.xlsx
@@ -40640,13 +40640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006E5CED-0A1E-433A-8362-D0D058E0E6B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32E151A3-CAA3-4504-8785-846E58DDB2DE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B4C36B3-A455-4AB4-9051-EBBD4C311DA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E78F7CBE-8D37-46AF-96D4-750993BC94D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4670682-DABF-4FCC-A312-D146C7AFFFB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027B1AC4-4326-49B5-9E67-CC42502EF6CD}"/>
 </file>
--- a/ksoft/docs/records/Stock_Group_Accounts.xlsx
+++ b/ksoft/docs/records/Stock_Group_Accounts.xlsx
@@ -40640,13 +40640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32E151A3-CAA3-4504-8785-846E58DDB2DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006E5CED-0A1E-433A-8362-D0D058E0E6B0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E78F7CBE-8D37-46AF-96D4-750993BC94D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B4C36B3-A455-4AB4-9051-EBBD4C311DA7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027B1AC4-4326-49B5-9E67-CC42502EF6CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4670682-DABF-4FCC-A312-D146C7AFFFB2}"/>
 </file>